--- a/Tool/data/Shop.xlsx
+++ b/Tool/data/Shop.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -15,12 +15,12 @@
     <sheet name="ShopProducts" sheetId="1" r:id="rId1"/>
     <sheet name="BundleContents" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="102">
   <si>
     <t>ProductID</t>
   </si>
@@ -70,45 +70,126 @@
     <t>SHOP_RARE_01</t>
   </si>
   <si>
+    <t>RareLimit</t>
+  </si>
+  <si>
+    <t>JadeShop</t>
+  </si>
+  <si>
+    <t>SingleItem</t>
+  </si>
+  <si>
+    <t>SunWukong</t>
+  </si>
+  <si>
+    <t>Jade</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
     <t>SHOP_RARE_02</t>
   </si>
   <si>
+    <t>Armor01_Belt</t>
+  </si>
+  <si>
+    <t>Lifetime</t>
+  </si>
+  <si>
     <t>SHOP_RARE_03</t>
   </si>
   <si>
+    <t>TangSanZang</t>
+  </si>
+  <si>
     <t>SHOP_RARE_04</t>
   </si>
   <si>
+    <t>common_exp</t>
+  </si>
+  <si>
+    <t>Weekly</t>
+  </si>
+  <si>
     <t>SHOP_RARE_05</t>
   </si>
   <si>
+    <t>Fried_Radish_Balls</t>
+  </si>
+  <si>
     <t>SHOP_RARE_06</t>
   </si>
   <si>
+    <t>Dragon_Bread_Noodies</t>
+  </si>
+  <si>
     <t>SHOP_RARE_07</t>
   </si>
   <si>
+    <t>CoinShop</t>
+  </si>
+  <si>
+    <t>Murshroom_Steamed_Buns</t>
+  </si>
+  <si>
+    <t>Coin</t>
+  </si>
+  <si>
     <t>SHOP_RARE_08</t>
   </si>
   <si>
+    <t>Tofu_Soup</t>
+  </si>
+  <si>
     <t>SHOP_RARE_09</t>
   </si>
   <si>
+    <t>Lamian_Noodies</t>
+  </si>
+  <si>
     <t>SHOP_RARE_10</t>
   </si>
   <si>
+    <t>fine_exp</t>
+  </si>
+  <si>
     <t>SHOP_RARE_11</t>
   </si>
   <si>
+    <t>rare_exp</t>
+  </si>
+  <si>
     <t>SHOP_RARE_12</t>
   </si>
   <si>
+    <t>ZhuBaJie</t>
+  </si>
+  <si>
     <t>SHOP_TIME_01</t>
   </si>
   <si>
+    <t>TimeSale</t>
+  </si>
+  <si>
+    <t>supreme_exp</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
     <t>SHOP_TIME_02</t>
   </si>
   <si>
+    <t>Garnet_Gemstone</t>
+  </si>
+  <si>
     <t>SHOP_TIME_03</t>
   </si>
   <si>
@@ -118,115 +199,70 @@
     <t>SHOP_COMBO_01</t>
   </si>
   <si>
+    <t>ComboPack</t>
+  </si>
+  <si>
+    <t>Bundle</t>
+  </si>
+  <si>
+    <t>BUNDLE_JADE_01</t>
+  </si>
+  <si>
     <t>SHOP_COMBO_02</t>
   </si>
   <si>
+    <t>BUNDLE_JADE_02</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
     <t>SHOP_COMBO_03</t>
   </si>
   <si>
+    <t>BUNDLE_COIN_01</t>
+  </si>
+  <si>
     <t>SHOP_COMBO_04</t>
   </si>
   <si>
-    <t>RareLimit</t>
-  </si>
-  <si>
-    <t>TimeSale</t>
-  </si>
-  <si>
-    <t>ComboPack</t>
-  </si>
-  <si>
-    <t>JadeShop</t>
-  </si>
-  <si>
-    <t>CoinShop</t>
-  </si>
-  <si>
-    <t>SingleItem</t>
-  </si>
-  <si>
-    <t>Bundle</t>
-  </si>
-  <si>
-    <t>SunWukong</t>
-  </si>
-  <si>
-    <t>Armor01_Belt</t>
-  </si>
-  <si>
-    <t>TangSanZang</t>
-  </si>
-  <si>
-    <t>common_exp</t>
-  </si>
-  <si>
-    <t>Fried_Radish_Balls</t>
-  </si>
-  <si>
-    <t>Dragon_Bread_Noodies</t>
-  </si>
-  <si>
-    <t>Murshroom_Steamed_Buns</t>
-  </si>
-  <si>
-    <t>Tofu_Soup</t>
-  </si>
-  <si>
-    <t>Lamian_Noodies</t>
-  </si>
-  <si>
-    <t>fine_exp</t>
-  </si>
-  <si>
-    <t>rare_exp</t>
-  </si>
-  <si>
-    <t>ZhuBaJie</t>
-  </si>
-  <si>
-    <t>supreme_exp</t>
-  </si>
-  <si>
-    <t>Garnet_Gemstone</t>
-  </si>
-  <si>
-    <t>BUNDLE_JADE_01</t>
-  </si>
-  <si>
-    <t>BUNDLE_JADE_02</t>
-  </si>
-  <si>
-    <t>BUNDLE_COIN_01</t>
-  </si>
-  <si>
     <t>BUNDLE_COIN_02</t>
   </si>
   <si>
-    <t>Jade</t>
-  </si>
-  <si>
-    <t>Coin</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>Lifetime</t>
-  </si>
-  <si>
-    <t>Weekly</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Monthly</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-30</t>
+    <t>SHOP_ARMOR_01_A</t>
+  </si>
+  <si>
+    <t>BUNDLE_ARMOR01_01</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_01_B</t>
+  </si>
+  <si>
+    <t>BUNDLE_ARMOR01_02</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_07_A</t>
+  </si>
+  <si>
+    <t>BUNDLE_ARMOR07_01</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_07_B</t>
+  </si>
+  <si>
+    <t>BUNDLE_ARMOR07_02</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_08_A</t>
+  </si>
+  <si>
+    <t>BUNDLE_ARMOR08_01</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_08_B</t>
+  </si>
+  <si>
+    <t>BUNDLE_ARMOR08_02</t>
   </si>
   <si>
     <t>BundleID</t>
@@ -239,13 +275,64 @@
   </si>
   <si>
     <t>Nimbus_Cudgel</t>
+  </si>
+  <si>
+    <t>Armor01_Helmet</t>
+  </si>
+  <si>
+    <t>Armor01_Chestplate</t>
+  </si>
+  <si>
+    <t>Armor01_Gloves</t>
+  </si>
+  <si>
+    <t>Armor01_Boots</t>
+  </si>
+  <si>
+    <t>Armor01_Ring</t>
+  </si>
+  <si>
+    <t>Armor07_Helmet</t>
+  </si>
+  <si>
+    <t>Armor07_Chestplate</t>
+  </si>
+  <si>
+    <t>Armor07_Gloves</t>
+  </si>
+  <si>
+    <t>Armor07_Boots</t>
+  </si>
+  <si>
+    <t>Armor07_Belt</t>
+  </si>
+  <si>
+    <t>Armor07_Ring</t>
+  </si>
+  <si>
+    <t>Armor08_Helmet</t>
+  </si>
+  <si>
+    <t>Armor08_Chestplate</t>
+  </si>
+  <si>
+    <t>Armor08_Gloves</t>
+  </si>
+  <si>
+    <t>Armor08_Boots</t>
+  </si>
+  <si>
+    <t>Armor08_Belt</t>
+  </si>
+  <si>
+    <t>Armor08_Ring</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -253,24 +340,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -278,29 +363,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -606,8 +682,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -661,843 +751,1089 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H2">
+        <v>19</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="2">
         <v>100</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>150</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H3">
+        <v>23</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2">
         <v>500</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>60</v>
-      </c>
-      <c r="H4">
+        <v>26</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="2">
         <v>10000</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>12000</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>5</v>
       </c>
       <c r="K4" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" t="s">
-        <v>40</v>
-      </c>
       <c r="E5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>60</v>
-      </c>
-      <c r="H5">
+        <v>28</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="2">
         <v>5000</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>5</v>
       </c>
       <c r="K5" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6">
+        <v>31</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="2">
         <v>1000</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>12000</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>1200</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>5</v>
       </c>
       <c r="K7" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="2">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2">
+        <v>150</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H8">
-        <v>100</v>
-      </c>
-      <c r="I8">
-        <v>150</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8" t="s">
-        <v>62</v>
-      </c>
       <c r="N8" t="b">
         <v>1</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
         <v>35</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
         <v>39</v>
       </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9">
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="2">
         <v>500</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>0</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="2">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
         <v>35</v>
       </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10">
+        <v>41</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="2">
         <v>10000</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>12000</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="2">
         <v>5</v>
       </c>
       <c r="K10" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
         <v>35</v>
       </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>61</v>
-      </c>
-      <c r="H11">
+        <v>43</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="2">
         <v>5000</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>0</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="2">
         <v>5</v>
       </c>
       <c r="K11" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
         <v>35</v>
       </c>
-      <c r="C12" t="s">
-        <v>39</v>
-      </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12">
+        <v>45</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="2">
         <v>1000</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>12000</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="2">
         <v>5</v>
       </c>
       <c r="K12" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
         <v>35</v>
       </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H13">
+        <v>47</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="2">
         <v>1200</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>0</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="2">
         <v>5</v>
       </c>
       <c r="K13" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14">
+        <v>50</v>
+      </c>
+      <c r="F14" s="3">
         <v>10</v>
       </c>
-      <c r="G14" t="s">
-        <v>60</v>
-      </c>
-      <c r="H14">
+      <c r="G14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2">
         <v>50</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>100</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="2">
         <v>5</v>
       </c>
       <c r="K14" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="L14" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="M14" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
         <v>55</v>
       </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>60</v>
-      </c>
-      <c r="H15">
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="2">
         <v>80</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>120</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="2">
         <v>5</v>
       </c>
       <c r="K15" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="L15" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="M15" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="3">
+        <v>10</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I16" s="2">
+        <v>8000</v>
+      </c>
+      <c r="J16" s="2">
+        <v>5</v>
+      </c>
+      <c r="K16" t="s">
         <v>51</v>
       </c>
-      <c r="F16">
-        <v>10</v>
-      </c>
-      <c r="G16" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16">
-        <v>5000</v>
-      </c>
-      <c r="I16">
-        <v>8000</v>
-      </c>
-      <c r="J16">
-        <v>5</v>
-      </c>
-      <c r="K16" t="s">
-        <v>65</v>
-      </c>
       <c r="L16" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="M16" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17">
+        <v>41</v>
+      </c>
+      <c r="F17" s="3">
         <v>5</v>
       </c>
-      <c r="G17" t="s">
-        <v>61</v>
-      </c>
-      <c r="H17">
+      <c r="G17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="2">
         <v>8000</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>10000</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="2">
         <v>5</v>
       </c>
       <c r="K17" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="L17" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="M17" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18" t="s">
-        <v>60</v>
-      </c>
-      <c r="H18">
+        <v>61</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="2">
         <v>300</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>500</v>
       </c>
-      <c r="J18">
-        <v>1</v>
+      <c r="J18" s="2">
+        <v>10</v>
       </c>
       <c r="K18" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
-        <v>60</v>
-      </c>
-      <c r="H19">
+        <v>63</v>
+      </c>
+      <c r="F19" s="3">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="2">
         <v>600</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>800</v>
       </c>
-      <c r="J19">
-        <v>1</v>
+      <c r="J19" s="2">
+        <v>10</v>
       </c>
       <c r="K19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20" t="s">
-        <v>61</v>
-      </c>
-      <c r="H20">
+      <c r="H20" s="2">
         <v>20000</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>30000</v>
       </c>
-      <c r="J20">
-        <v>1</v>
+      <c r="J20" s="2">
+        <v>10</v>
       </c>
       <c r="K20" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="B21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C21" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" t="s">
-        <v>41</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="H21" s="2">
+        <v>50000</v>
+      </c>
+      <c r="I21" s="2">
+        <v>70000</v>
+      </c>
+      <c r="J21" s="2">
+        <v>10</v>
+      </c>
+      <c r="K21" t="s">
+        <v>64</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" t="s">
         <v>59</v>
       </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21" t="s">
-        <v>61</v>
-      </c>
-      <c r="H21">
-        <v>50000</v>
-      </c>
-      <c r="I21">
-        <v>70000</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21" t="s">
-        <v>66</v>
-      </c>
-      <c r="N21" t="b">
-        <v>1</v>
-      </c>
-      <c r="O21">
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="2">
+        <v>800</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1200</v>
+      </c>
+      <c r="J22" s="2">
+        <v>10</v>
+      </c>
+      <c r="K22" t="s">
+        <v>29</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="2">
+        <v>800</v>
+      </c>
+      <c r="I23" s="2">
+        <v>1200</v>
+      </c>
+      <c r="J23" s="2">
+        <v>10</v>
+      </c>
+      <c r="K23" t="s">
+        <v>29</v>
+      </c>
+      <c r="N23" t="b">
+        <v>1</v>
+      </c>
+      <c r="O23" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="2">
+        <v>800</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1200</v>
+      </c>
+      <c r="J24" s="2">
+        <v>10</v>
+      </c>
+      <c r="K24" t="s">
+        <v>29</v>
+      </c>
+      <c r="N24" t="b">
+        <v>1</v>
+      </c>
+      <c r="O24" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="2">
+        <v>800</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1200</v>
+      </c>
+      <c r="J25" s="2">
+        <v>10</v>
+      </c>
+      <c r="K25" t="s">
+        <v>29</v>
+      </c>
+      <c r="N25" t="b">
+        <v>1</v>
+      </c>
+      <c r="O25" s="2">
         <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="2">
+        <v>800</v>
+      </c>
+      <c r="I26" s="2">
+        <v>1200</v>
+      </c>
+      <c r="J26" s="2">
+        <v>10</v>
+      </c>
+      <c r="K26" t="s">
+        <v>29</v>
+      </c>
+      <c r="N26" t="b">
+        <v>1</v>
+      </c>
+      <c r="O26" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" t="s">
+        <v>80</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="2">
+        <v>800</v>
+      </c>
+      <c r="I27" s="2">
+        <v>1200</v>
+      </c>
+      <c r="J27" s="2">
+        <v>10</v>
+      </c>
+      <c r="K27" t="s">
+        <v>29</v>
+      </c>
+      <c r="N27" t="b">
+        <v>1</v>
+      </c>
+      <c r="O27" s="2">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1507,7 +1843,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -1515,22 +1851,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>71</v>
+      <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -1538,10 +1874,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -1549,10 +1885,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -1560,7 +1896,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -1571,10 +1907,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1582,7 +1918,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -1593,10 +1929,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -1604,10 +1940,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -1615,10 +1951,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C10">
         <v>20</v>
@@ -1626,10 +1962,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>5</v>
@@ -1637,10 +1973,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -1648,10 +1984,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>10</v>
@@ -1659,10 +1995,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C14">
         <v>50</v>
@@ -1670,13 +2006,211 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C15">
         <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Tool/data/Shop.xlsx
+++ b/Tool/data/Shop.xlsx
@@ -9,18 +9,20 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="ShopProducts" sheetId="1" r:id="rId1"/>
     <sheet name="BundleContents" sheetId="2" r:id="rId2"/>
+    <sheet name="SevenDayLogin" sheetId="3" r:id="rId3"/>
+    <sheet name="RedeemCode" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="235">
   <si>
     <t>ProductID</t>
   </si>
@@ -67,228 +69,585 @@
     <t>SortOrder</t>
   </si>
   <si>
-    <t>SHOP_RARE_01</t>
+    <t>SHOP_COIN_EXP_01</t>
   </si>
   <si>
     <t>RareLimit</t>
   </si>
   <si>
+    <t>CoinShop</t>
+  </si>
+  <si>
+    <t>SingleItem</t>
+  </si>
+  <si>
+    <t>fine_exp</t>
+  </si>
+  <si>
+    <t>Coin</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>SHOP_COIN_EXP_02</t>
+  </si>
+  <si>
+    <t>rare_exp</t>
+  </si>
+  <si>
+    <t>SHOP_COIN_ENERGY_01</t>
+  </si>
+  <si>
+    <t>Murshroom_Steamed_Buns</t>
+  </si>
+  <si>
+    <t>SHOP_COIN_GEM_GARNET</t>
+  </si>
+  <si>
+    <t>Garnet_Sliver</t>
+  </si>
+  <si>
+    <t>SHOP_COIN_GEM_LAPIS</t>
+  </si>
+  <si>
+    <t>Lapis_Lazuli_Sliver</t>
+  </si>
+  <si>
+    <t>SHOP_COIN_GEM_AMETHYST</t>
+  </si>
+  <si>
+    <t>Amethyst_Sliver</t>
+  </si>
+  <si>
+    <t>SHOP_COIN_GEM_YELLOW</t>
+  </si>
+  <si>
+    <t>Yellow_Jade_Sliver</t>
+  </si>
+  <si>
+    <t>SHOP_COIN_GEM_TOPAZ</t>
+  </si>
+  <si>
+    <t>Topaz_Sliver</t>
+  </si>
+  <si>
+    <t>SHOP_COIN_GEM_JADE</t>
+  </si>
+  <si>
+    <t>Jade_Sliver</t>
+  </si>
+  <si>
+    <t>SHOP_COIN_GEM_AQUA</t>
+  </si>
+  <si>
+    <t>Aquamarine_Sliver</t>
+  </si>
+  <si>
+    <t>SHOP_COIN_ESSENCE_01</t>
+  </si>
+  <si>
+    <t>RelicEssence</t>
+  </si>
+  <si>
+    <t>SHOP_COIN_PRIMORITE_01</t>
+  </si>
+  <si>
+    <t>ArmorPrimorite</t>
+  </si>
+  <si>
+    <t>SHOP_COIN_FOOD_01</t>
+  </si>
+  <si>
+    <t>Lamian_Noodies</t>
+  </si>
+  <si>
+    <t>SHOP_COIN_FOOD_02</t>
+  </si>
+  <si>
+    <t>Fried_Radish_Balls</t>
+  </si>
+  <si>
+    <t>SHOP_COIN_FOOD_03</t>
+  </si>
+  <si>
+    <t>Tofu_Soup</t>
+  </si>
+  <si>
+    <t>SHOP_COIN_SHARD_SANZANG</t>
+  </si>
+  <si>
+    <t>TangSanZang</t>
+  </si>
+  <si>
+    <t>SHOP_COIN_SHARD_WUJING</t>
+  </si>
+  <si>
+    <t>ShaWujing</t>
+  </si>
+  <si>
+    <t>SHOP_JADE_TICKET_01</t>
+  </si>
+  <si>
     <t>JadeShop</t>
   </si>
   <si>
-    <t>SingleItem</t>
+    <t>Ticket</t>
+  </si>
+  <si>
+    <t>Jade</t>
+  </si>
+  <si>
+    <t>SHOP_JADE_TICKET_10</t>
+  </si>
+  <si>
+    <t>Weekly</t>
+  </si>
+  <si>
+    <t>SHOP_JADE_FOOD_DUMPLING</t>
+  </si>
+  <si>
+    <t>Shirmp_Dumplings</t>
+  </si>
+  <si>
+    <t>SHOP_JADE_EXP_SUPREME</t>
+  </si>
+  <si>
+    <t>supreme_exp</t>
+  </si>
+  <si>
+    <t>SHOP_JADE_SHARD_WUKONG</t>
   </si>
   <si>
     <t>SunWukong</t>
   </si>
   <si>
-    <t>Jade</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>SHOP_RARE_02</t>
+    <t>SHOP_JADE_SHARD_NEZHA</t>
+  </si>
+  <si>
+    <t>ThirdPrinceNezha</t>
+  </si>
+  <si>
+    <t>SHOP_JADE_SHARD_ERLANG</t>
+  </si>
+  <si>
+    <t>ErlangShen</t>
+  </si>
+  <si>
+    <t>SHOP_JADE_SHARD_BULL</t>
+  </si>
+  <si>
+    <t>BullDemonKing</t>
+  </si>
+  <si>
+    <t>SHOP_JADE_SHARD_LIJING</t>
+  </si>
+  <si>
+    <t>LiJing</t>
+  </si>
+  <si>
+    <t>SHOP_JADE_FOOD_CRIT</t>
+  </si>
+  <si>
+    <t>Jade_Parcels</t>
+  </si>
+  <si>
+    <t>SHOP_JADE_FOOD_RES</t>
+  </si>
+  <si>
+    <t>Dragon_Bread_Noodies</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_COIN_FRAG_GARNET</t>
+  </si>
+  <si>
+    <t>TimeSale</t>
+  </si>
+  <si>
+    <t>Garnet_Fragment</t>
+  </si>
+  <si>
+    <t>2026-01-01</t>
+  </si>
+  <si>
+    <t>2026-12-31</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_COIN_FRAG_LAPIS</t>
+  </si>
+  <si>
+    <t>Lapis_Lazuli_Fragment</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_COIN_FRAG_AMETHYST</t>
+  </si>
+  <si>
+    <t>Amethyst_Fragment</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_COIN_FRAG_YELLOW</t>
+  </si>
+  <si>
+    <t>Yellow_Jade_Fragment</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_COIN_FRAG_TOPAZ</t>
+  </si>
+  <si>
+    <t>Topaz_Fragment</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_COIN_FRAG_JADE</t>
+  </si>
+  <si>
+    <t>Jade_Fragment</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_COIN_FRAG_AQUA</t>
+  </si>
+  <si>
+    <t>Aquamarine_Fragment</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_COIN_MAT_SLIME</t>
+  </si>
+  <si>
+    <t>Slime</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_COIN_MAT_MEAT</t>
+  </si>
+  <si>
+    <t>Meat</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_COIN_MAT_PEACH</t>
+  </si>
+  <si>
+    <t>Peach</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_COIN_MAT_LOTUS</t>
+  </si>
+  <si>
+    <t>Lotus</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_JADE_CHUNK_GARNET</t>
+  </si>
+  <si>
+    <t>Garnet_Chunk</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_JADE_CHUNK_LAPIS</t>
+  </si>
+  <si>
+    <t>Lapis_Lazuli_Chunk</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_JADE_CHUNK_AMETHYST</t>
+  </si>
+  <si>
+    <t>Amethyst_Chunk</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_JADE_CHUNK_YELLOW</t>
+  </si>
+  <si>
+    <t>Yellow_Jade_Chunk</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_JADE_GEM_GARNET</t>
+  </si>
+  <si>
+    <t>Garnet_Gemstone</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_JADE_GEM_LAPIS</t>
+  </si>
+  <si>
+    <t>Lapis_Lazuli_Gemstone</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_JADE_GEM_AMETHYST</t>
+  </si>
+  <si>
+    <t>Amethyst_Gemstone</t>
+  </si>
+  <si>
+    <t>SHOP_TIME_JADE_GEM_YELLOW</t>
+  </si>
+  <si>
+    <t>Yellow_Jade_Gemstone</t>
+  </si>
+  <si>
+    <t>SHOP_COMBO_DAY1</t>
+  </si>
+  <si>
+    <t>ComboPack</t>
+  </si>
+  <si>
+    <t>Bundle</t>
+  </si>
+  <si>
+    <t>BUNDLE_DAY1_STARTER</t>
+  </si>
+  <si>
+    <t>Lifetime</t>
+  </si>
+  <si>
+    <t>SHOP_COMBO_DAY2</t>
+  </si>
+  <si>
+    <t>BUNDLE_DAY2_WEAPON</t>
+  </si>
+  <si>
+    <t>SHOP_COMBO_DAY3</t>
+  </si>
+  <si>
+    <t>BUNDLE_DAY3_SSR</t>
+  </si>
+  <si>
+    <t>SHOP_COMBO_DAY4</t>
+  </si>
+  <si>
+    <t>BUNDLE_DAY4_ASCEND</t>
+  </si>
+  <si>
+    <t>SHOP_COMBO_DAY5</t>
+  </si>
+  <si>
+    <t>BUNDLE_DAY5_ARMOR</t>
+  </si>
+  <si>
+    <t>SHOP_COMBO_DAY6</t>
+  </si>
+  <si>
+    <t>BUNDLE_DAY6_UR</t>
+  </si>
+  <si>
+    <t>SHOP_COMBO_DAY7</t>
+  </si>
+  <si>
+    <t>BUNDLE_DAY7_ENDGAME</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_Armor05_A</t>
+  </si>
+  <si>
+    <t>BUNDLE_Armor05_A</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_Armor05_B</t>
+  </si>
+  <si>
+    <t>BUNDLE_Armor05_B</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_Armor03_A</t>
+  </si>
+  <si>
+    <t>BUNDLE_Armor03_A</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_Armor03_B</t>
+  </si>
+  <si>
+    <t>BUNDLE_Armor03_B</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_Armor02_A</t>
+  </si>
+  <si>
+    <t>BUNDLE_Armor02_A</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_Armor02_B</t>
+  </si>
+  <si>
+    <t>BUNDLE_Armor02_B</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_Armor04_A</t>
+  </si>
+  <si>
+    <t>BUNDLE_Armor04_A</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_Armor04_B</t>
+  </si>
+  <si>
+    <t>BUNDLE_Armor04_B</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_Armor06_A</t>
+  </si>
+  <si>
+    <t>BUNDLE_Armor06_A</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_Armor06_B</t>
+  </si>
+  <si>
+    <t>BUNDLE_Armor06_B</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_Armor01_A</t>
+  </si>
+  <si>
+    <t>BUNDLE_Armor01_A</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_Armor01_B</t>
+  </si>
+  <si>
+    <t>BUNDLE_Armor01_B</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_Armor07_A</t>
+  </si>
+  <si>
+    <t>BUNDLE_Armor07_A</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_Armor07_B</t>
+  </si>
+  <si>
+    <t>BUNDLE_Armor07_B</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_Armor08_A</t>
+  </si>
+  <si>
+    <t>BUNDLE_Armor08_A</t>
+  </si>
+  <si>
+    <t>SHOP_ARMOR_Armor08_B</t>
+  </si>
+  <si>
+    <t>BUNDLE_Armor08_B</t>
+  </si>
+  <si>
+    <t>BundleID</t>
+  </si>
+  <si>
+    <t>ItemID</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>common_exp</t>
+  </si>
+  <si>
+    <t>ZhuBaJie</t>
+  </si>
+  <si>
+    <t>Armor04_Helmet</t>
+  </si>
+  <si>
+    <t>Armor04_Chestplate</t>
+  </si>
+  <si>
+    <t>Armor04_Gloves</t>
+  </si>
+  <si>
+    <t>Armor05_Helmet</t>
+  </si>
+  <si>
+    <t>Armor05_Chestplate</t>
+  </si>
+  <si>
+    <t>Armor05_Gloves</t>
+  </si>
+  <si>
+    <t>Armor05_Boots</t>
+  </si>
+  <si>
+    <t>Armor05_Belt</t>
+  </si>
+  <si>
+    <t>Armor05_Ring</t>
+  </si>
+  <si>
+    <t>Armor03_Helmet</t>
+  </si>
+  <si>
+    <t>Armor03_Chestplate</t>
+  </si>
+  <si>
+    <t>Armor03_Gloves</t>
+  </si>
+  <si>
+    <t>Armor03_Boots</t>
+  </si>
+  <si>
+    <t>Armor03_Belt</t>
+  </si>
+  <si>
+    <t>Armor03_Ring</t>
+  </si>
+  <si>
+    <t>Armor02_Helmet</t>
+  </si>
+  <si>
+    <t>Armor02_Chestplate</t>
+  </si>
+  <si>
+    <t>Armor02_Gloves</t>
+  </si>
+  <si>
+    <t>Armor02_Boots</t>
+  </si>
+  <si>
+    <t>Armor02_Belt</t>
+  </si>
+  <si>
+    <t>Armor02_Ring</t>
+  </si>
+  <si>
+    <t>Armor04_Boots</t>
+  </si>
+  <si>
+    <t>Armor04_Belt</t>
+  </si>
+  <si>
+    <t>Armor04_Ring</t>
+  </si>
+  <si>
+    <t>Armor06_Helmet</t>
+  </si>
+  <si>
+    <t>Armor06_Chestplate</t>
+  </si>
+  <si>
+    <t>Armor06_Gloves</t>
+  </si>
+  <si>
+    <t>Armor06_Boots</t>
+  </si>
+  <si>
+    <t>Armor06_Belt</t>
+  </si>
+  <si>
+    <t>Armor06_Ring</t>
+  </si>
+  <si>
+    <t>Armor01_Helmet</t>
+  </si>
+  <si>
+    <t>Armor01_Chestplate</t>
+  </si>
+  <si>
+    <t>Armor01_Gloves</t>
+  </si>
+  <si>
+    <t>Armor01_Boots</t>
   </si>
   <si>
     <t>Armor01_Belt</t>
   </si>
   <si>
-    <t>Lifetime</t>
-  </si>
-  <si>
-    <t>SHOP_RARE_03</t>
-  </si>
-  <si>
-    <t>TangSanZang</t>
-  </si>
-  <si>
-    <t>SHOP_RARE_04</t>
-  </si>
-  <si>
-    <t>common_exp</t>
-  </si>
-  <si>
-    <t>Weekly</t>
-  </si>
-  <si>
-    <t>SHOP_RARE_05</t>
-  </si>
-  <si>
-    <t>Fried_Radish_Balls</t>
-  </si>
-  <si>
-    <t>SHOP_RARE_06</t>
-  </si>
-  <si>
-    <t>Dragon_Bread_Noodies</t>
-  </si>
-  <si>
-    <t>SHOP_RARE_07</t>
-  </si>
-  <si>
-    <t>CoinShop</t>
-  </si>
-  <si>
-    <t>Murshroom_Steamed_Buns</t>
-  </si>
-  <si>
-    <t>Coin</t>
-  </si>
-  <si>
-    <t>SHOP_RARE_08</t>
-  </si>
-  <si>
-    <t>Tofu_Soup</t>
-  </si>
-  <si>
-    <t>SHOP_RARE_09</t>
-  </si>
-  <si>
-    <t>Lamian_Noodies</t>
-  </si>
-  <si>
-    <t>SHOP_RARE_10</t>
-  </si>
-  <si>
-    <t>fine_exp</t>
-  </si>
-  <si>
-    <t>SHOP_RARE_11</t>
-  </si>
-  <si>
-    <t>rare_exp</t>
-  </si>
-  <si>
-    <t>SHOP_RARE_12</t>
-  </si>
-  <si>
-    <t>ZhuBaJie</t>
-  </si>
-  <si>
-    <t>SHOP_TIME_01</t>
-  </si>
-  <si>
-    <t>TimeSale</t>
-  </si>
-  <si>
-    <t>supreme_exp</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-30</t>
-  </si>
-  <si>
-    <t>SHOP_TIME_02</t>
-  </si>
-  <si>
-    <t>Garnet_Gemstone</t>
-  </si>
-  <si>
-    <t>SHOP_TIME_03</t>
-  </si>
-  <si>
-    <t>SHOP_TIME_04</t>
-  </si>
-  <si>
-    <t>SHOP_COMBO_01</t>
-  </si>
-  <si>
-    <t>ComboPack</t>
-  </si>
-  <si>
-    <t>Bundle</t>
-  </si>
-  <si>
-    <t>BUNDLE_JADE_01</t>
-  </si>
-  <si>
-    <t>SHOP_COMBO_02</t>
-  </si>
-  <si>
-    <t>BUNDLE_JADE_02</t>
-  </si>
-  <si>
-    <t>Monthly</t>
-  </si>
-  <si>
-    <t>SHOP_COMBO_03</t>
-  </si>
-  <si>
-    <t>BUNDLE_COIN_01</t>
-  </si>
-  <si>
-    <t>SHOP_COMBO_04</t>
-  </si>
-  <si>
-    <t>BUNDLE_COIN_02</t>
-  </si>
-  <si>
-    <t>SHOP_ARMOR_01_A</t>
-  </si>
-  <si>
-    <t>BUNDLE_ARMOR01_01</t>
-  </si>
-  <si>
-    <t>SHOP_ARMOR_01_B</t>
-  </si>
-  <si>
-    <t>BUNDLE_ARMOR01_02</t>
-  </si>
-  <si>
-    <t>SHOP_ARMOR_07_A</t>
-  </si>
-  <si>
-    <t>BUNDLE_ARMOR07_01</t>
-  </si>
-  <si>
-    <t>SHOP_ARMOR_07_B</t>
-  </si>
-  <si>
-    <t>BUNDLE_ARMOR07_02</t>
-  </si>
-  <si>
-    <t>SHOP_ARMOR_08_A</t>
-  </si>
-  <si>
-    <t>BUNDLE_ARMOR08_01</t>
-  </si>
-  <si>
-    <t>SHOP_ARMOR_08_B</t>
-  </si>
-  <si>
-    <t>BUNDLE_ARMOR08_02</t>
-  </si>
-  <si>
-    <t>BundleID</t>
-  </si>
-  <si>
-    <t>ItemID</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>Nimbus_Cudgel</t>
-  </si>
-  <si>
-    <t>Armor01_Helmet</t>
-  </si>
-  <si>
-    <t>Armor01_Chestplate</t>
-  </si>
-  <si>
-    <t>Armor01_Gloves</t>
-  </si>
-  <si>
-    <t>Armor01_Boots</t>
-  </si>
-  <si>
     <t>Armor01_Ring</t>
   </si>
   <si>
@@ -326,6 +685,48 @@
   </si>
   <si>
     <t>Armor08_Ring</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>RewardID</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Character</t>
+  </si>
+  <si>
+    <t>Weapon</t>
+  </si>
+  <si>
+    <t>Triple_Edged_Blade</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>GIFT_COIN</t>
+  </si>
+  <si>
+    <t>GIFT_JADE</t>
+  </si>
+  <si>
+    <t>GIFT_RELIC</t>
+  </si>
+  <si>
+    <t>GIFT_ARMOR</t>
+  </si>
+  <si>
+    <t>GIFT_TICKET</t>
   </si>
 </sst>
 </file>
@@ -341,7 +742,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -351,6 +752,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -375,8 +782,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -682,10 +1089,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -695,7 +1102,8 @@
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" customWidth="1"/>
     <col min="15" max="15" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -762,20 +1170,20 @@
       <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="F2">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="2">
-        <v>100</v>
-      </c>
-      <c r="I2" s="2">
-        <v>150</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1</v>
+      <c r="H2">
+        <v>20000</v>
+      </c>
+      <c r="I2">
+        <v>25000</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
       </c>
       <c r="K2" t="s">
         <v>21</v>
@@ -783,7 +1191,7 @@
       <c r="N2" t="b">
         <v>1</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2">
         <v>1</v>
       </c>
     </row>
@@ -803,34 +1211,34 @@
       <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="F3">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2">
-        <v>500</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1</v>
+      <c r="H3">
+        <v>35000</v>
+      </c>
+      <c r="I3">
+        <v>45000</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
@@ -842,22 +1250,22 @@
         <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="2">
-        <v>10000</v>
-      </c>
-      <c r="I4" s="2">
-        <v>12000</v>
-      </c>
-      <c r="J4" s="2">
-        <v>5</v>
+      <c r="H4">
+        <v>15000</v>
+      </c>
+      <c r="I4">
+        <v>20000</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
       </c>
       <c r="K4" t="s">
         <v>21</v>
@@ -865,13 +1273,13 @@
       <c r="N4" t="b">
         <v>1</v>
       </c>
-      <c r="O4" s="2">
+      <c r="O4">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
@@ -883,36 +1291,36 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
-        <v>5</v>
+      <c r="H5">
+        <v>20000</v>
+      </c>
+      <c r="I5">
+        <v>25000</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
       </c>
-      <c r="O5" s="2">
+      <c r="O5">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
@@ -924,22 +1332,22 @@
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I6" s="2">
-        <v>12000</v>
-      </c>
-      <c r="J6" s="2">
-        <v>5</v>
+      <c r="H6">
+        <v>20000</v>
+      </c>
+      <c r="I6">
+        <v>25000</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
       </c>
       <c r="K6" t="s">
         <v>21</v>
@@ -947,13 +1355,13 @@
       <c r="N6" t="b">
         <v>1</v>
       </c>
-      <c r="O6" s="2">
-        <v>3</v>
+      <c r="O6">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -965,63 +1373,63 @@
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="2">
-        <v>1200</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>5</v>
+      <c r="H7">
+        <v>20000</v>
+      </c>
+      <c r="I7">
+        <v>25000</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
       </c>
       <c r="K7" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
       </c>
-      <c r="O7" s="2">
-        <v>4</v>
+      <c r="O7">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="2">
-        <v>100</v>
-      </c>
-      <c r="I8" s="2">
-        <v>150</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8">
+        <v>20000</v>
+      </c>
+      <c r="I8">
+        <v>25000</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
       </c>
       <c r="K8" t="s">
         <v>21</v>
@@ -1029,81 +1437,81 @@
       <c r="N8" t="b">
         <v>1</v>
       </c>
-      <c r="O8" s="2">
-        <v>1</v>
+      <c r="O8">
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="2">
-        <v>500</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9">
+        <v>20000</v>
+      </c>
+      <c r="I9">
+        <v>25000</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
       </c>
       <c r="K9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
       </c>
-      <c r="O9" s="2">
-        <v>2</v>
+      <c r="O9">
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="2">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="2">
-        <v>12000</v>
-      </c>
-      <c r="J10" s="2">
-        <v>5</v>
+      <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10">
+        <v>20000</v>
+      </c>
+      <c r="I10">
+        <v>25000</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
       </c>
       <c r="K10" t="s">
         <v>21</v>
@@ -1111,81 +1519,81 @@
       <c r="N10" t="b">
         <v>1</v>
       </c>
-      <c r="O10" s="2">
-        <v>3</v>
+      <c r="O10">
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2">
-        <v>5</v>
+        <v>39</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11">
+        <v>20000</v>
+      </c>
+      <c r="I11">
+        <v>25000</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
       </c>
       <c r="K11" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
       </c>
-      <c r="O11" s="2">
-        <v>4</v>
+      <c r="O11">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="2">
+        <v>41</v>
+      </c>
+      <c r="F12">
         <v>1000</v>
       </c>
-      <c r="I12" s="2">
-        <v>12000</v>
-      </c>
-      <c r="J12" s="2">
-        <v>5</v>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12">
+        <v>30000</v>
+      </c>
+      <c r="I12">
+        <v>40000</v>
+      </c>
+      <c r="J12">
+        <v>3</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -1193,57 +1601,57 @@
       <c r="N12" t="b">
         <v>1</v>
       </c>
-      <c r="O12" s="2">
-        <v>3</v>
+      <c r="O12">
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
-      </c>
-      <c r="F13" s="3">
-        <v>1</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1200</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2">
-        <v>5</v>
+        <v>43</v>
+      </c>
+      <c r="F13">
+        <v>500</v>
+      </c>
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13">
+        <v>25000</v>
+      </c>
+      <c r="I13">
+        <v>35000</v>
+      </c>
+      <c r="J13">
+        <v>3</v>
       </c>
       <c r="K13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
       </c>
-      <c r="O13" s="2">
-        <v>4</v>
+      <c r="O13">
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
         <v>17</v>
@@ -1252,45 +1660,39 @@
         <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="3">
-        <v>10</v>
-      </c>
-      <c r="G14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="2">
-        <v>50</v>
-      </c>
-      <c r="I14" s="2">
-        <v>100</v>
-      </c>
-      <c r="J14" s="2">
-        <v>5</v>
+      <c r="H14">
+        <v>5000</v>
+      </c>
+      <c r="I14">
+        <v>6000</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
       </c>
       <c r="K14" t="s">
-        <v>51</v>
-      </c>
-      <c r="L14" t="s">
-        <v>52</v>
-      </c>
-      <c r="M14" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
       </c>
-      <c r="O14" s="2">
-        <v>1</v>
+      <c r="O14">
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -1299,541 +1701,2441 @@
         <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="2">
-        <v>80</v>
-      </c>
-      <c r="I15" s="2">
-        <v>120</v>
-      </c>
-      <c r="J15" s="2">
-        <v>5</v>
+      <c r="H15">
+        <v>4000</v>
+      </c>
+      <c r="I15">
+        <v>5000</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
       </c>
       <c r="K15" t="s">
-        <v>51</v>
-      </c>
-      <c r="L15" t="s">
-        <v>52</v>
-      </c>
-      <c r="M15" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
       </c>
-      <c r="O15" s="2">
-        <v>2</v>
+      <c r="O15">
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="3">
-        <v>10</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H16" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I16" s="2">
-        <v>8000</v>
-      </c>
-      <c r="J16" s="2">
-        <v>5</v>
+        <v>49</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16">
+        <v>6000</v>
+      </c>
+      <c r="I16">
+        <v>7500</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
       </c>
       <c r="K16" t="s">
-        <v>51</v>
-      </c>
-      <c r="L16" t="s">
-        <v>52</v>
-      </c>
-      <c r="M16" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
       </c>
-      <c r="O16" s="2">
-        <v>3</v>
+      <c r="O16">
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="3">
-        <v>5</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H17" s="2">
-        <v>8000</v>
-      </c>
-      <c r="I17" s="2">
+        <v>51</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17">
         <v>10000</v>
       </c>
-      <c r="J17" s="2">
-        <v>5</v>
+      <c r="I17">
+        <v>12000</v>
+      </c>
+      <c r="J17">
+        <v>3</v>
       </c>
       <c r="K17" t="s">
-        <v>51</v>
-      </c>
-      <c r="L17" t="s">
-        <v>52</v>
-      </c>
-      <c r="M17" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
       </c>
-      <c r="O17" s="2">
-        <v>4</v>
+      <c r="O17">
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="E18" t="s">
-        <v>61</v>
-      </c>
-      <c r="F18" s="3">
-        <v>1</v>
-      </c>
-      <c r="G18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="2">
-        <v>300</v>
-      </c>
-      <c r="I18" s="2">
-        <v>500</v>
-      </c>
-      <c r="J18" s="2">
-        <v>10</v>
+      <c r="H18">
+        <v>10000</v>
+      </c>
+      <c r="I18">
+        <v>12000</v>
+      </c>
+      <c r="J18">
+        <v>3</v>
       </c>
       <c r="K18" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
       </c>
-      <c r="O18" s="2">
-        <v>1</v>
+      <c r="O18">
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
-      </c>
-      <c r="F19" s="3">
-        <v>1</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="2">
-        <v>600</v>
-      </c>
-      <c r="I19" s="2">
-        <v>800</v>
-      </c>
-      <c r="J19" s="2">
+        <v>56</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>57</v>
+      </c>
+      <c r="H19">
+        <v>160</v>
+      </c>
+      <c r="I19">
+        <v>160</v>
+      </c>
+      <c r="J19">
         <v>10</v>
       </c>
       <c r="K19" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
       </c>
-      <c r="O19" s="2">
-        <v>2</v>
+      <c r="O19">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20">
+        <v>10</v>
+      </c>
+      <c r="G20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20">
+        <v>1440</v>
+      </c>
+      <c r="I20">
+        <v>1600</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20" t="s">
         <v>59</v>
       </c>
-      <c r="C20" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" t="s">
-        <v>60</v>
-      </c>
-      <c r="E20" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H20" s="2">
-        <v>20000</v>
-      </c>
-      <c r="I20" s="2">
-        <v>30000</v>
-      </c>
-      <c r="J20" s="2">
-        <v>10</v>
-      </c>
-      <c r="K20" t="s">
-        <v>29</v>
-      </c>
       <c r="N20" t="b">
         <v>1</v>
       </c>
-      <c r="O20" s="2">
-        <v>3</v>
+      <c r="O20">
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H21" s="2">
-        <v>50000</v>
-      </c>
-      <c r="I21" s="2">
-        <v>70000</v>
-      </c>
-      <c r="J21" s="2">
-        <v>10</v>
+        <v>61</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" t="s">
+        <v>57</v>
+      </c>
+      <c r="H21">
+        <v>100</v>
+      </c>
+      <c r="I21">
+        <v>120</v>
+      </c>
+      <c r="J21">
+        <v>3</v>
       </c>
       <c r="K21" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
       </c>
-      <c r="O21" s="2">
-        <v>4</v>
+      <c r="O21">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="E22" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="2">
-        <v>800</v>
-      </c>
-      <c r="I22" s="2">
-        <v>1200</v>
-      </c>
-      <c r="J22" s="2">
+        <v>63</v>
+      </c>
+      <c r="F22">
         <v>10</v>
       </c>
+      <c r="G22" t="s">
+        <v>57</v>
+      </c>
+      <c r="H22">
+        <v>300</v>
+      </c>
+      <c r="I22">
+        <v>400</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
       <c r="K22" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
       </c>
-      <c r="O22" s="2">
-        <v>1</v>
+      <c r="O22">
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23" t="s">
+        <v>57</v>
+      </c>
+      <c r="H23">
+        <v>450</v>
+      </c>
+      <c r="I23">
+        <v>500</v>
+      </c>
+      <c r="J23">
+        <v>4</v>
+      </c>
+      <c r="K23" t="s">
         <v>59</v>
       </c>
-      <c r="C23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" t="s">
-        <v>60</v>
-      </c>
-      <c r="E23" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="2">
-        <v>800</v>
-      </c>
-      <c r="I23" s="2">
-        <v>1200</v>
-      </c>
-      <c r="J23" s="2">
-        <v>10</v>
-      </c>
-      <c r="K23" t="s">
-        <v>29</v>
-      </c>
       <c r="N23" t="b">
         <v>1</v>
       </c>
-      <c r="O23" s="2">
-        <v>2</v>
+      <c r="O23">
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24" t="s">
+        <v>57</v>
+      </c>
+      <c r="H24">
+        <v>450</v>
+      </c>
+      <c r="I24">
+        <v>500</v>
+      </c>
+      <c r="J24">
+        <v>4</v>
+      </c>
+      <c r="K24" t="s">
         <v>59</v>
       </c>
-      <c r="C24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" t="s">
-        <v>60</v>
-      </c>
-      <c r="E24" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="2">
-        <v>800</v>
-      </c>
-      <c r="I24" s="2">
-        <v>1200</v>
-      </c>
-      <c r="J24" s="2">
-        <v>10</v>
-      </c>
-      <c r="K24" t="s">
-        <v>29</v>
-      </c>
       <c r="N24" t="b">
         <v>1</v>
       </c>
-      <c r="O24" s="2">
-        <v>3</v>
+      <c r="O24">
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25" t="s">
+        <v>57</v>
+      </c>
+      <c r="H25">
+        <v>450</v>
+      </c>
+      <c r="I25">
+        <v>500</v>
+      </c>
+      <c r="J25">
+        <v>4</v>
+      </c>
+      <c r="K25" t="s">
         <v>59</v>
       </c>
-      <c r="C25" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" t="s">
-        <v>76</v>
-      </c>
-      <c r="F25" s="3">
-        <v>1</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25" s="2">
-        <v>800</v>
-      </c>
-      <c r="I25" s="2">
-        <v>1200</v>
-      </c>
-      <c r="J25" s="2">
-        <v>10</v>
-      </c>
-      <c r="K25" t="s">
-        <v>29</v>
-      </c>
       <c r="N25" t="b">
         <v>1</v>
       </c>
-      <c r="O25" s="2">
-        <v>4</v>
+      <c r="O25">
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26" t="s">
+        <v>57</v>
+      </c>
+      <c r="H26">
+        <v>450</v>
+      </c>
+      <c r="I26">
+        <v>500</v>
+      </c>
+      <c r="J26">
+        <v>4</v>
+      </c>
+      <c r="K26" t="s">
         <v>59</v>
       </c>
-      <c r="C26" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" t="s">
-        <v>60</v>
-      </c>
-      <c r="E26" t="s">
-        <v>78</v>
-      </c>
-      <c r="F26" s="3">
-        <v>1</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H26" s="2">
-        <v>800</v>
-      </c>
-      <c r="I26" s="2">
-        <v>1200</v>
-      </c>
-      <c r="J26" s="2">
-        <v>10</v>
-      </c>
-      <c r="K26" t="s">
-        <v>29</v>
-      </c>
       <c r="N26" t="b">
         <v>1</v>
       </c>
-      <c r="O26" s="2">
-        <v>5</v>
+      <c r="O26">
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27" t="s">
+        <v>57</v>
+      </c>
+      <c r="H27">
+        <v>450</v>
+      </c>
+      <c r="I27">
+        <v>500</v>
+      </c>
+      <c r="J27">
+        <v>4</v>
+      </c>
+      <c r="K27" t="s">
+        <v>59</v>
+      </c>
+      <c r="N27" t="b">
+        <v>1</v>
+      </c>
+      <c r="O27">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28" t="s">
+        <v>57</v>
+      </c>
+      <c r="H28">
+        <v>150</v>
+      </c>
+      <c r="I28">
+        <v>200</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="K28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N28" t="b">
+        <v>1</v>
+      </c>
+      <c r="O28">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s">
+        <v>77</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29" t="s">
+        <v>57</v>
+      </c>
+      <c r="H29">
+        <v>150</v>
+      </c>
+      <c r="I29">
+        <v>200</v>
+      </c>
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="K29" t="s">
+        <v>21</v>
+      </c>
+      <c r="N29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O29">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" t="s">
         <v>79</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" t="s">
+        <v>80</v>
+      </c>
+      <c r="F30">
+        <v>8</v>
+      </c>
+      <c r="G30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30">
+        <v>35000</v>
+      </c>
+      <c r="I30">
+        <v>45000</v>
+      </c>
+      <c r="J30">
+        <v>2</v>
+      </c>
+      <c r="K30" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" t="s">
+        <v>81</v>
+      </c>
+      <c r="M30" t="s">
+        <v>82</v>
+      </c>
+      <c r="N30" t="b">
+        <v>1</v>
+      </c>
+      <c r="O30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" t="s">
+        <v>84</v>
+      </c>
+      <c r="F31">
+        <v>8</v>
+      </c>
+      <c r="G31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31">
+        <v>35000</v>
+      </c>
+      <c r="I31">
+        <v>45000</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="K31" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" t="s">
+        <v>81</v>
+      </c>
+      <c r="M31" t="s">
+        <v>82</v>
+      </c>
+      <c r="N31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" t="s">
+        <v>86</v>
+      </c>
+      <c r="F32">
+        <v>8</v>
+      </c>
+      <c r="G32" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32">
+        <v>35000</v>
+      </c>
+      <c r="I32">
+        <v>45000</v>
+      </c>
+      <c r="J32">
+        <v>2</v>
+      </c>
+      <c r="K32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" t="s">
+        <v>81</v>
+      </c>
+      <c r="M32" t="s">
+        <v>82</v>
+      </c>
+      <c r="N32" t="b">
+        <v>1</v>
+      </c>
+      <c r="O32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" t="s">
+        <v>88</v>
+      </c>
+      <c r="F33">
+        <v>8</v>
+      </c>
+      <c r="G33" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33">
+        <v>35000</v>
+      </c>
+      <c r="I33">
+        <v>45000</v>
+      </c>
+      <c r="J33">
+        <v>2</v>
+      </c>
+      <c r="K33" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" t="s">
+        <v>81</v>
+      </c>
+      <c r="M33" t="s">
+        <v>82</v>
+      </c>
+      <c r="N33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s">
+        <v>90</v>
+      </c>
+      <c r="F34">
+        <v>8</v>
+      </c>
+      <c r="G34" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34">
+        <v>35000</v>
+      </c>
+      <c r="I34">
+        <v>45000</v>
+      </c>
+      <c r="J34">
+        <v>2</v>
+      </c>
+      <c r="K34" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" t="s">
+        <v>81</v>
+      </c>
+      <c r="M34" t="s">
+        <v>82</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" t="s">
+        <v>92</v>
+      </c>
+      <c r="F35">
+        <v>8</v>
+      </c>
+      <c r="G35" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35">
+        <v>35000</v>
+      </c>
+      <c r="I35">
+        <v>45000</v>
+      </c>
+      <c r="J35">
+        <v>2</v>
+      </c>
+      <c r="K35" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" t="s">
+        <v>81</v>
+      </c>
+      <c r="M35" t="s">
+        <v>82</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
+      </c>
+      <c r="O35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36">
+        <v>8</v>
+      </c>
+      <c r="G36" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36">
+        <v>35000</v>
+      </c>
+      <c r="I36">
+        <v>45000</v>
+      </c>
+      <c r="J36">
+        <v>2</v>
+      </c>
+      <c r="K36" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" t="s">
+        <v>81</v>
+      </c>
+      <c r="M36" t="s">
+        <v>82</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
+      </c>
+      <c r="O36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" t="s">
+        <v>96</v>
+      </c>
+      <c r="F37">
+        <v>10</v>
+      </c>
+      <c r="G37" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37">
+        <v>10000</v>
+      </c>
+      <c r="I37">
+        <v>12000</v>
+      </c>
+      <c r="J37">
+        <v>5</v>
+      </c>
+      <c r="K37" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" t="s">
+        <v>81</v>
+      </c>
+      <c r="M37" t="s">
+        <v>82</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
+      </c>
+      <c r="O37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" t="s">
+        <v>98</v>
+      </c>
+      <c r="F38">
+        <v>10</v>
+      </c>
+      <c r="G38" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38">
+        <v>15000</v>
+      </c>
+      <c r="I38">
+        <v>20000</v>
+      </c>
+      <c r="J38">
+        <v>5</v>
+      </c>
+      <c r="K38" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" t="s">
+        <v>81</v>
+      </c>
+      <c r="M38" t="s">
+        <v>82</v>
+      </c>
+      <c r="N38" t="b">
+        <v>1</v>
+      </c>
+      <c r="O38">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" t="s">
+        <v>100</v>
+      </c>
+      <c r="F39">
+        <v>10</v>
+      </c>
+      <c r="G39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H39">
+        <v>20000</v>
+      </c>
+      <c r="I39">
+        <v>25000</v>
+      </c>
+      <c r="J39">
+        <v>5</v>
+      </c>
+      <c r="K39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" t="s">
+        <v>81</v>
+      </c>
+      <c r="M39" t="s">
+        <v>82</v>
+      </c>
+      <c r="N39" t="b">
+        <v>1</v>
+      </c>
+      <c r="O39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>101</v>
+      </c>
+      <c r="B40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" t="s">
+        <v>102</v>
+      </c>
+      <c r="F40">
+        <v>10</v>
+      </c>
+      <c r="G40" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40">
+        <v>25000</v>
+      </c>
+      <c r="I40">
+        <v>30000</v>
+      </c>
+      <c r="J40">
+        <v>5</v>
+      </c>
+      <c r="K40" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" t="s">
+        <v>81</v>
+      </c>
+      <c r="M40" t="s">
+        <v>82</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
+      </c>
+      <c r="O40">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" t="s">
+        <v>104</v>
+      </c>
+      <c r="F41">
+        <v>6</v>
+      </c>
+      <c r="G41" t="s">
+        <v>57</v>
+      </c>
+      <c r="H41">
+        <v>250</v>
+      </c>
+      <c r="I41">
+        <v>350</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" t="s">
+        <v>81</v>
+      </c>
+      <c r="M41" t="s">
+        <v>82</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
+      </c>
+      <c r="O41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>105</v>
+      </c>
+      <c r="B42" t="s">
+        <v>79</v>
+      </c>
+      <c r="C42" t="s">
+        <v>55</v>
+      </c>
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" t="s">
+        <v>106</v>
+      </c>
+      <c r="F42">
+        <v>6</v>
+      </c>
+      <c r="G42" t="s">
+        <v>57</v>
+      </c>
+      <c r="H42">
+        <v>250</v>
+      </c>
+      <c r="I42">
+        <v>350</v>
+      </c>
+      <c r="J42">
+        <v>2</v>
+      </c>
+      <c r="K42" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" t="s">
+        <v>81</v>
+      </c>
+      <c r="M42" t="s">
+        <v>82</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
+      </c>
+      <c r="O42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>107</v>
+      </c>
+      <c r="B43" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" t="s">
+        <v>108</v>
+      </c>
+      <c r="F43">
+        <v>6</v>
+      </c>
+      <c r="G43" t="s">
+        <v>57</v>
+      </c>
+      <c r="H43">
+        <v>250</v>
+      </c>
+      <c r="I43">
+        <v>350</v>
+      </c>
+      <c r="J43">
+        <v>2</v>
+      </c>
+      <c r="K43" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" t="s">
+        <v>81</v>
+      </c>
+      <c r="M43" t="s">
+        <v>82</v>
+      </c>
+      <c r="N43" t="b">
+        <v>1</v>
+      </c>
+      <c r="O43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>109</v>
+      </c>
+      <c r="B44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44" t="s">
+        <v>55</v>
+      </c>
+      <c r="D44" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" t="s">
+        <v>110</v>
+      </c>
+      <c r="F44">
+        <v>6</v>
+      </c>
+      <c r="G44" t="s">
+        <v>57</v>
+      </c>
+      <c r="H44">
+        <v>250</v>
+      </c>
+      <c r="I44">
+        <v>350</v>
+      </c>
+      <c r="J44">
+        <v>2</v>
+      </c>
+      <c r="K44" t="s">
+        <v>21</v>
+      </c>
+      <c r="L44" t="s">
+        <v>81</v>
+      </c>
+      <c r="M44" t="s">
+        <v>82</v>
+      </c>
+      <c r="N44" t="b">
+        <v>1</v>
+      </c>
+      <c r="O44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>111</v>
+      </c>
+      <c r="B45" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" t="s">
+        <v>112</v>
+      </c>
+      <c r="F45">
+        <v>4</v>
+      </c>
+      <c r="G45" t="s">
+        <v>57</v>
+      </c>
+      <c r="H45">
+        <v>400</v>
+      </c>
+      <c r="I45">
+        <v>550</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45" t="s">
+        <v>21</v>
+      </c>
+      <c r="L45" t="s">
+        <v>81</v>
+      </c>
+      <c r="M45" t="s">
+        <v>82</v>
+      </c>
+      <c r="N45" t="b">
+        <v>1</v>
+      </c>
+      <c r="O45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" t="s">
+        <v>55</v>
+      </c>
+      <c r="D46" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" t="s">
+        <v>114</v>
+      </c>
+      <c r="F46">
+        <v>4</v>
+      </c>
+      <c r="G46" t="s">
+        <v>57</v>
+      </c>
+      <c r="H46">
+        <v>400</v>
+      </c>
+      <c r="I46">
+        <v>550</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="K46" t="s">
+        <v>21</v>
+      </c>
+      <c r="L46" t="s">
+        <v>81</v>
+      </c>
+      <c r="M46" t="s">
+        <v>82</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
+      </c>
+      <c r="O46">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" t="s">
+        <v>55</v>
+      </c>
+      <c r="D47" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" t="s">
+        <v>116</v>
+      </c>
+      <c r="F47">
+        <v>4</v>
+      </c>
+      <c r="G47" t="s">
+        <v>57</v>
+      </c>
+      <c r="H47">
+        <v>400</v>
+      </c>
+      <c r="I47">
+        <v>550</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47" t="s">
+        <v>21</v>
+      </c>
+      <c r="L47" t="s">
+        <v>81</v>
+      </c>
+      <c r="M47" t="s">
+        <v>82</v>
+      </c>
+      <c r="N47" t="b">
+        <v>1</v>
+      </c>
+      <c r="O47">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>117</v>
+      </c>
+      <c r="B48" t="s">
+        <v>79</v>
+      </c>
+      <c r="C48" t="s">
+        <v>55</v>
+      </c>
+      <c r="D48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" t="s">
+        <v>118</v>
+      </c>
+      <c r="F48">
+        <v>4</v>
+      </c>
+      <c r="G48" t="s">
+        <v>57</v>
+      </c>
+      <c r="H48">
+        <v>400</v>
+      </c>
+      <c r="I48">
+        <v>550</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48" t="s">
+        <v>21</v>
+      </c>
+      <c r="L48" t="s">
+        <v>81</v>
+      </c>
+      <c r="M48" t="s">
+        <v>82</v>
+      </c>
+      <c r="N48" t="b">
+        <v>1</v>
+      </c>
+      <c r="O48">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>119</v>
+      </c>
+      <c r="B49" t="s">
+        <v>120</v>
+      </c>
+      <c r="C49" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" t="s">
+        <v>121</v>
+      </c>
+      <c r="E49" t="s">
+        <v>122</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49">
+        <v>25000</v>
+      </c>
+      <c r="I49">
+        <v>50000</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49" t="s">
+        <v>123</v>
+      </c>
+      <c r="N49" t="b">
+        <v>1</v>
+      </c>
+      <c r="O49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>124</v>
+      </c>
+      <c r="B50" t="s">
+        <v>120</v>
+      </c>
+      <c r="C50" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50" t="s">
+        <v>121</v>
+      </c>
+      <c r="E50" t="s">
+        <v>125</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50" t="s">
+        <v>57</v>
+      </c>
+      <c r="H50">
+        <v>250</v>
+      </c>
+      <c r="I50">
+        <v>400</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50" t="s">
+        <v>123</v>
+      </c>
+      <c r="N50" t="b">
+        <v>1</v>
+      </c>
+      <c r="O50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>126</v>
+      </c>
+      <c r="B51" t="s">
+        <v>120</v>
+      </c>
+      <c r="C51" t="s">
+        <v>55</v>
+      </c>
+      <c r="D51" t="s">
+        <v>121</v>
+      </c>
+      <c r="E51" t="s">
+        <v>127</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51" t="s">
+        <v>57</v>
+      </c>
+      <c r="H51">
+        <v>480</v>
+      </c>
+      <c r="I51">
+        <v>750</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51" t="s">
+        <v>123</v>
+      </c>
+      <c r="N51" t="b">
+        <v>1</v>
+      </c>
+      <c r="O51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>128</v>
+      </c>
+      <c r="B52" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" t="s">
+        <v>55</v>
+      </c>
+      <c r="D52" t="s">
+        <v>121</v>
+      </c>
+      <c r="E52" t="s">
+        <v>129</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52" t="s">
+        <v>57</v>
+      </c>
+      <c r="H52">
+        <v>550</v>
+      </c>
+      <c r="I52">
+        <v>850</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+      <c r="K52" t="s">
+        <v>123</v>
+      </c>
+      <c r="N52" t="b">
+        <v>1</v>
+      </c>
+      <c r="O52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>130</v>
+      </c>
+      <c r="B53" t="s">
+        <v>120</v>
+      </c>
+      <c r="C53" t="s">
+        <v>55</v>
+      </c>
+      <c r="D53" t="s">
+        <v>121</v>
+      </c>
+      <c r="E53" t="s">
+        <v>131</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53" t="s">
+        <v>57</v>
+      </c>
+      <c r="H53">
+        <v>750</v>
+      </c>
+      <c r="I53">
+        <v>1200</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53" t="s">
+        <v>123</v>
+      </c>
+      <c r="N53" t="b">
+        <v>1</v>
+      </c>
+      <c r="O53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>132</v>
+      </c>
+      <c r="B54" t="s">
+        <v>120</v>
+      </c>
+      <c r="C54" t="s">
+        <v>55</v>
+      </c>
+      <c r="D54" t="s">
+        <v>121</v>
+      </c>
+      <c r="E54" t="s">
+        <v>133</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54" t="s">
+        <v>57</v>
+      </c>
+      <c r="H54">
+        <v>1000</v>
+      </c>
+      <c r="I54">
+        <v>1600</v>
+      </c>
+      <c r="J54">
+        <v>1</v>
+      </c>
+      <c r="K54" t="s">
+        <v>123</v>
+      </c>
+      <c r="N54" t="b">
+        <v>1</v>
+      </c>
+      <c r="O54">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>134</v>
+      </c>
+      <c r="B55" t="s">
+        <v>120</v>
+      </c>
+      <c r="C55" t="s">
+        <v>55</v>
+      </c>
+      <c r="D55" t="s">
+        <v>121</v>
+      </c>
+      <c r="E55" t="s">
+        <v>135</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55" t="s">
+        <v>57</v>
+      </c>
+      <c r="H55">
+        <v>1400</v>
+      </c>
+      <c r="I55">
+        <v>2500</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55" t="s">
+        <v>123</v>
+      </c>
+      <c r="N55" t="b">
+        <v>1</v>
+      </c>
+      <c r="O55">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>136</v>
+      </c>
+      <c r="B56" t="s">
+        <v>120</v>
+      </c>
+      <c r="C56" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" t="s">
+        <v>121</v>
+      </c>
+      <c r="E56" t="s">
+        <v>137</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56" t="s">
+        <v>20</v>
+      </c>
+      <c r="H56">
+        <v>20000</v>
+      </c>
+      <c r="I56">
+        <v>28000</v>
+      </c>
+      <c r="J56">
+        <v>5</v>
+      </c>
+      <c r="K56" t="s">
         <v>59</v>
       </c>
-      <c r="C27" t="s">
+      <c r="N56" t="b">
+        <v>1</v>
+      </c>
+      <c r="O56">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>138</v>
+      </c>
+      <c r="B57" t="s">
+        <v>120</v>
+      </c>
+      <c r="C57" t="s">
         <v>17</v>
       </c>
-      <c r="D27" t="s">
-        <v>60</v>
-      </c>
-      <c r="E27" t="s">
-        <v>80</v>
-      </c>
-      <c r="F27" s="3">
-        <v>1</v>
-      </c>
-      <c r="G27" s="3" t="s">
+      <c r="D57" t="s">
+        <v>121</v>
+      </c>
+      <c r="E57" t="s">
+        <v>139</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57" t="s">
         <v>20</v>
       </c>
-      <c r="H27" s="2">
-        <v>800</v>
-      </c>
-      <c r="I27" s="2">
-        <v>1200</v>
-      </c>
-      <c r="J27" s="2">
-        <v>10</v>
-      </c>
-      <c r="K27" t="s">
+      <c r="H57">
+        <v>20000</v>
+      </c>
+      <c r="I57">
+        <v>28000</v>
+      </c>
+      <c r="J57">
+        <v>5</v>
+      </c>
+      <c r="K57" t="s">
+        <v>59</v>
+      </c>
+      <c r="N57" t="b">
+        <v>1</v>
+      </c>
+      <c r="O57">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>140</v>
+      </c>
+      <c r="B58" t="s">
+        <v>120</v>
+      </c>
+      <c r="C58" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" t="s">
+        <v>121</v>
+      </c>
+      <c r="E58" t="s">
+        <v>141</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58" t="s">
+        <v>20</v>
+      </c>
+      <c r="H58">
+        <v>45000</v>
+      </c>
+      <c r="I58">
+        <v>65000</v>
+      </c>
+      <c r="J58">
+        <v>5</v>
+      </c>
+      <c r="K58" t="s">
+        <v>59</v>
+      </c>
+      <c r="N58" t="b">
+        <v>1</v>
+      </c>
+      <c r="O58">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>142</v>
+      </c>
+      <c r="B59" t="s">
+        <v>120</v>
+      </c>
+      <c r="C59" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" t="s">
+        <v>121</v>
+      </c>
+      <c r="E59" t="s">
+        <v>143</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59" t="s">
+        <v>20</v>
+      </c>
+      <c r="H59">
+        <v>45000</v>
+      </c>
+      <c r="I59">
+        <v>65000</v>
+      </c>
+      <c r="J59">
+        <v>5</v>
+      </c>
+      <c r="K59" t="s">
+        <v>59</v>
+      </c>
+      <c r="N59" t="b">
+        <v>1</v>
+      </c>
+      <c r="O59">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>144</v>
+      </c>
+      <c r="B60" t="s">
+        <v>120</v>
+      </c>
+      <c r="C60" t="s">
+        <v>17</v>
+      </c>
+      <c r="D60" t="s">
+        <v>121</v>
+      </c>
+      <c r="E60" t="s">
+        <v>145</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60" t="s">
+        <v>20</v>
+      </c>
+      <c r="H60">
+        <v>90000</v>
+      </c>
+      <c r="I60">
+        <v>130000</v>
+      </c>
+      <c r="J60">
+        <v>5</v>
+      </c>
+      <c r="K60" t="s">
+        <v>59</v>
+      </c>
+      <c r="N60" t="b">
+        <v>1</v>
+      </c>
+      <c r="O60">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>146</v>
+      </c>
+      <c r="B61" t="s">
+        <v>120</v>
+      </c>
+      <c r="C61" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" t="s">
+        <v>121</v>
+      </c>
+      <c r="E61" t="s">
+        <v>147</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61" t="s">
+        <v>20</v>
+      </c>
+      <c r="H61">
+        <v>90000</v>
+      </c>
+      <c r="I61">
+        <v>130000</v>
+      </c>
+      <c r="J61">
+        <v>5</v>
+      </c>
+      <c r="K61" t="s">
+        <v>59</v>
+      </c>
+      <c r="N61" t="b">
+        <v>1</v>
+      </c>
+      <c r="O61">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>148</v>
+      </c>
+      <c r="B62" t="s">
+        <v>120</v>
+      </c>
+      <c r="C62" t="s">
+        <v>55</v>
+      </c>
+      <c r="D62" t="s">
+        <v>121</v>
+      </c>
+      <c r="E62" t="s">
+        <v>149</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62" t="s">
+        <v>57</v>
+      </c>
+      <c r="H62">
+        <v>350</v>
+      </c>
+      <c r="I62">
+        <v>550</v>
+      </c>
+      <c r="J62">
+        <v>3</v>
+      </c>
+      <c r="K62" t="s">
+        <v>59</v>
+      </c>
+      <c r="N62" t="b">
+        <v>1</v>
+      </c>
+      <c r="O62">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>150</v>
+      </c>
+      <c r="B63" t="s">
+        <v>120</v>
+      </c>
+      <c r="C63" t="s">
+        <v>55</v>
+      </c>
+      <c r="D63" t="s">
+        <v>121</v>
+      </c>
+      <c r="E63" t="s">
+        <v>151</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63" t="s">
+        <v>57</v>
+      </c>
+      <c r="H63">
+        <v>220</v>
+      </c>
+      <c r="I63">
+        <v>350</v>
+      </c>
+      <c r="J63">
+        <v>3</v>
+      </c>
+      <c r="K63" t="s">
+        <v>59</v>
+      </c>
+      <c r="N63" t="b">
+        <v>1</v>
+      </c>
+      <c r="O63">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>152</v>
+      </c>
+      <c r="B64" t="s">
+        <v>120</v>
+      </c>
+      <c r="C64" t="s">
+        <v>55</v>
+      </c>
+      <c r="D64" t="s">
+        <v>121</v>
+      </c>
+      <c r="E64" t="s">
+        <v>153</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64" t="s">
+        <v>57</v>
+      </c>
+      <c r="H64">
+        <v>350</v>
+      </c>
+      <c r="I64">
+        <v>550</v>
+      </c>
+      <c r="J64">
+        <v>3</v>
+      </c>
+      <c r="K64" t="s">
+        <v>59</v>
+      </c>
+      <c r="N64" t="b">
+        <v>1</v>
+      </c>
+      <c r="O64">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>154</v>
+      </c>
+      <c r="B65" t="s">
+        <v>120</v>
+      </c>
+      <c r="C65" t="s">
+        <v>55</v>
+      </c>
+      <c r="D65" t="s">
+        <v>121</v>
+      </c>
+      <c r="E65" t="s">
+        <v>155</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65" t="s">
+        <v>57</v>
+      </c>
+      <c r="H65">
+        <v>220</v>
+      </c>
+      <c r="I65">
+        <v>350</v>
+      </c>
+      <c r="J65">
+        <v>3</v>
+      </c>
+      <c r="K65" t="s">
+        <v>59</v>
+      </c>
+      <c r="N65" t="b">
+        <v>1</v>
+      </c>
+      <c r="O65">
         <v>29</v>
       </c>
-      <c r="N27" t="b">
-        <v>1</v>
-      </c>
-      <c r="O27" s="2">
-        <v>6</v>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>156</v>
+      </c>
+      <c r="B66" t="s">
+        <v>120</v>
+      </c>
+      <c r="C66" t="s">
+        <v>55</v>
+      </c>
+      <c r="D66" t="s">
+        <v>121</v>
+      </c>
+      <c r="E66" t="s">
+        <v>157</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66" t="s">
+        <v>57</v>
+      </c>
+      <c r="H66">
+        <v>550</v>
+      </c>
+      <c r="I66">
+        <v>850</v>
+      </c>
+      <c r="J66">
+        <v>3</v>
+      </c>
+      <c r="K66" t="s">
+        <v>59</v>
+      </c>
+      <c r="N66" t="b">
+        <v>1</v>
+      </c>
+      <c r="O66">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>158</v>
+      </c>
+      <c r="B67" t="s">
+        <v>120</v>
+      </c>
+      <c r="C67" t="s">
+        <v>55</v>
+      </c>
+      <c r="D67" t="s">
+        <v>121</v>
+      </c>
+      <c r="E67" t="s">
+        <v>159</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67" t="s">
+        <v>57</v>
+      </c>
+      <c r="H67">
+        <v>380</v>
+      </c>
+      <c r="I67">
+        <v>600</v>
+      </c>
+      <c r="J67">
+        <v>3</v>
+      </c>
+      <c r="K67" t="s">
+        <v>59</v>
+      </c>
+      <c r="N67" t="b">
+        <v>1</v>
+      </c>
+      <c r="O67">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>160</v>
+      </c>
+      <c r="B68" t="s">
+        <v>120</v>
+      </c>
+      <c r="C68" t="s">
+        <v>55</v>
+      </c>
+      <c r="D68" t="s">
+        <v>121</v>
+      </c>
+      <c r="E68" t="s">
+        <v>161</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68" t="s">
+        <v>57</v>
+      </c>
+      <c r="H68">
+        <v>550</v>
+      </c>
+      <c r="I68">
+        <v>850</v>
+      </c>
+      <c r="J68">
+        <v>3</v>
+      </c>
+      <c r="K68" t="s">
+        <v>59</v>
+      </c>
+      <c r="N68" t="b">
+        <v>1</v>
+      </c>
+      <c r="O68">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>162</v>
+      </c>
+      <c r="B69" t="s">
+        <v>120</v>
+      </c>
+      <c r="C69" t="s">
+        <v>55</v>
+      </c>
+      <c r="D69" t="s">
+        <v>121</v>
+      </c>
+      <c r="E69" t="s">
+        <v>163</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69" t="s">
+        <v>57</v>
+      </c>
+      <c r="H69">
+        <v>380</v>
+      </c>
+      <c r="I69">
+        <v>600</v>
+      </c>
+      <c r="J69">
+        <v>3</v>
+      </c>
+      <c r="K69" t="s">
+        <v>59</v>
+      </c>
+      <c r="N69" t="b">
+        <v>1</v>
+      </c>
+      <c r="O69">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>164</v>
+      </c>
+      <c r="B70" t="s">
+        <v>120</v>
+      </c>
+      <c r="C70" t="s">
+        <v>55</v>
+      </c>
+      <c r="D70" t="s">
+        <v>121</v>
+      </c>
+      <c r="E70" t="s">
+        <v>165</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70" t="s">
+        <v>57</v>
+      </c>
+      <c r="H70">
+        <v>550</v>
+      </c>
+      <c r="I70">
+        <v>850</v>
+      </c>
+      <c r="J70">
+        <v>3</v>
+      </c>
+      <c r="K70" t="s">
+        <v>59</v>
+      </c>
+      <c r="N70" t="b">
+        <v>1</v>
+      </c>
+      <c r="O70">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>166</v>
+      </c>
+      <c r="B71" t="s">
+        <v>120</v>
+      </c>
+      <c r="C71" t="s">
+        <v>55</v>
+      </c>
+      <c r="D71" t="s">
+        <v>121</v>
+      </c>
+      <c r="E71" t="s">
+        <v>167</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71" t="s">
+        <v>57</v>
+      </c>
+      <c r="H71">
+        <v>380</v>
+      </c>
+      <c r="I71">
+        <v>600</v>
+      </c>
+      <c r="J71">
+        <v>3</v>
+      </c>
+      <c r="K71" t="s">
+        <v>59</v>
+      </c>
+      <c r="N71" t="b">
+        <v>1</v>
+      </c>
+      <c r="O71">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1843,184 +4145,184 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.85546875" customWidth="1"/>
     <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>168</v>
       </c>
       <c r="B1" t="s">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="C1" t="s">
-        <v>83</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>172</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C10">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="C14">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>174</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -2028,10 +4330,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>175</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2039,87 +4341,87 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>131</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -2127,10 +4429,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>177</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -2138,10 +4440,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -2149,10 +4451,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -2160,10 +4462,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>180</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -2171,10 +4473,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>181</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -2182,10 +4484,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>182</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -2193,10 +4495,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -2204,16 +4506,726 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>184</v>
       </c>
       <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>143</v>
+      </c>
+      <c r="B34" t="s">
+        <v>185</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>143</v>
+      </c>
+      <c r="B35" t="s">
+        <v>186</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>143</v>
+      </c>
+      <c r="B36" t="s">
+        <v>187</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>145</v>
+      </c>
+      <c r="B37" t="s">
+        <v>188</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>145</v>
+      </c>
+      <c r="B38" t="s">
+        <v>189</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39" t="s">
+        <v>190</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" t="s">
+        <v>191</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>147</v>
+      </c>
+      <c r="B41" t="s">
+        <v>192</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>147</v>
+      </c>
+      <c r="B42" t="s">
+        <v>193</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>149</v>
+      </c>
+      <c r="B43" t="s">
+        <v>173</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>149</v>
+      </c>
+      <c r="B44" t="s">
+        <v>174</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>149</v>
+      </c>
+      <c r="B45" t="s">
+        <v>175</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>149</v>
+      </c>
+      <c r="B46" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>151</v>
+      </c>
+      <c r="B47" t="s">
+        <v>194</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>151</v>
+      </c>
+      <c r="B48" t="s">
+        <v>195</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>151</v>
+      </c>
+      <c r="B49" t="s">
+        <v>196</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>153</v>
+      </c>
+      <c r="B50" t="s">
+        <v>197</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" t="s">
+        <v>198</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>153</v>
+      </c>
+      <c r="B52" t="s">
+        <v>199</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>153</v>
+      </c>
+      <c r="B53" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>155</v>
+      </c>
+      <c r="B54" t="s">
+        <v>200</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>155</v>
+      </c>
+      <c r="B55" t="s">
+        <v>201</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>155</v>
+      </c>
+      <c r="B56" t="s">
+        <v>202</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>157</v>
+      </c>
+      <c r="B57" t="s">
+        <v>203</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>157</v>
+      </c>
+      <c r="B58" t="s">
+        <v>204</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>157</v>
+      </c>
+      <c r="B59" t="s">
+        <v>205</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>157</v>
+      </c>
+      <c r="B60" t="s">
+        <v>43</v>
+      </c>
+      <c r="C60">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>159</v>
+      </c>
+      <c r="B61" t="s">
+        <v>206</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>159</v>
+      </c>
+      <c r="B62" t="s">
+        <v>207</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>159</v>
+      </c>
+      <c r="B63" t="s">
+        <v>208</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>161</v>
+      </c>
+      <c r="B64" t="s">
+        <v>209</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>161</v>
+      </c>
+      <c r="B65" t="s">
+        <v>210</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>161</v>
+      </c>
+      <c r="B66" t="s">
+        <v>211</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>161</v>
+      </c>
+      <c r="B67" t="s">
+        <v>43</v>
+      </c>
+      <c r="C67">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>163</v>
+      </c>
+      <c r="B68" t="s">
+        <v>212</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>163</v>
+      </c>
+      <c r="B69" t="s">
+        <v>213</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>163</v>
+      </c>
+      <c r="B70" t="s">
+        <v>214</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>165</v>
+      </c>
+      <c r="B71" t="s">
+        <v>215</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>165</v>
+      </c>
+      <c r="B72" t="s">
+        <v>216</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>165</v>
+      </c>
+      <c r="B73" t="s">
+        <v>217</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>165</v>
+      </c>
+      <c r="B74" t="s">
+        <v>43</v>
+      </c>
+      <c r="C74">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>167</v>
+      </c>
+      <c r="B75" t="s">
+        <v>218</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>167</v>
+      </c>
+      <c r="B76" t="s">
+        <v>219</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>167</v>
+      </c>
+      <c r="B77" t="s">
+        <v>220</v>
+      </c>
+      <c r="C77">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="2">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>100000</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3">
+        <v>2000</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4">
+        <v>5000</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5">
+        <v>5000</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Tool/data/Shop.xlsx
+++ b/Tool/data/Shop.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="236">
   <si>
     <t>ProductID</t>
   </si>
@@ -727,6 +727,9 @@
   </si>
   <si>
     <t>GIFT_TICKET</t>
+  </si>
+  <si>
+    <t>`</t>
   </si>
 </sst>
 </file>
@@ -1102,8 +1105,8 @@
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" customWidth="1"/>
     <col min="15" max="15" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5120,10 +5123,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>229</v>
       </c>
@@ -5140,7 +5146,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>230</v>
       </c>
@@ -5151,13 +5157,13 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>100000</v>
+        <v>2009000</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>231</v>
       </c>
@@ -5168,13 +5174,13 @@
         <v>57</v>
       </c>
       <c r="D3">
-        <v>2000</v>
+        <v>109000</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>232</v>
       </c>
@@ -5185,13 +5191,13 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>5000</v>
+        <v>100900</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>233</v>
       </c>
@@ -5202,13 +5208,13 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>234</v>
       </c>
@@ -5219,10 +5225,15 @@
         <v>56</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K12" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/Tool/data/Shop.xlsx
+++ b/Tool/data/Shop.xlsx
@@ -777,7 +777,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -787,6 +787,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5126,23 +5129,25 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5157,7 +5162,7 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>2009000</v>
+        <v>1000000</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -5174,7 +5179,7 @@
         <v>57</v>
       </c>
       <c r="D3">
-        <v>109000</v>
+        <v>100000</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -5191,7 +5196,7 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>100900</v>
+        <v>100000</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -5208,7 +5213,7 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>

--- a/Tool/data/Shop.xlsx
+++ b/Tool/data/Shop.xlsx
@@ -5131,7 +5131,7 @@
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5162,7 +5162,7 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>1000000</v>
+        <v>10000000</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>

--- a/Tool/data/Shop.xlsx
+++ b/Tool/data/Shop.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityUdeme\MyTemplate\MyTemplate\Tool\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityUdeme\Trunk_Android\MyTemplateAndroid\MyTemplate_Android\Tool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -5230,7 +5230,7 @@
         <v>56</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>

--- a/Tool/data/Shop.xlsx
+++ b/Tool/data/Shop.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityUdeme\Trunk_Android\MyTemplateAndroid\MyTemplate_Android\Tool\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityUdeme\MyTemplate\MyTemplate\Tool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
     <sheet name="SevenDayLogin" sheetId="3" r:id="rId3"/>
     <sheet name="RedeemCode" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="237">
   <si>
     <t>ProductID</t>
   </si>
@@ -730,6 +730,9 @@
   </si>
   <si>
     <t>`</t>
+  </si>
+  <si>
+    <t>GIFT_EXP</t>
   </si>
 </sst>
 </file>
@@ -5129,7 +5132,7 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
     <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -5155,7 +5158,7 @@
       <c r="A2" t="s">
         <v>230</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>224</v>
       </c>
       <c r="C2" t="s">
@@ -5172,7 +5175,7 @@
       <c r="A3" t="s">
         <v>231</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>224</v>
       </c>
       <c r="C3" t="s">
@@ -5189,7 +5192,7 @@
       <c r="A4" t="s">
         <v>232</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>224</v>
       </c>
       <c r="C4" t="s">
@@ -5206,7 +5209,7 @@
       <c r="A5" t="s">
         <v>233</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>224</v>
       </c>
       <c r="C5" t="s">
@@ -5223,7 +5226,7 @@
       <c r="A6" t="s">
         <v>234</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>224</v>
       </c>
       <c r="C6" t="s">
@@ -5233,6 +5236,23 @@
         <v>100</v>
       </c>
       <c r="E6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>236</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+      <c r="E7" t="b">
         <v>1</v>
       </c>
     </row>
